--- a/artfynd/A 59469-2025 artfynd.xlsx
+++ b/artfynd/A 59469-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4961357</v>
+        <v>2436303</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387673.3663582579</v>
+        <v>387673</v>
       </c>
       <c r="R2" t="n">
-        <v>6568588.077439586</v>
+        <v>6568588</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5287184</v>
+        <v>2436304</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>eskilns ostsida 1,4 km syd Ekholmen, Vrm</t>
+          <t>Eskilns sydostsida, 1,5 km syd Ekholmen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387673.3663582579</v>
+        <v>387525</v>
       </c>
       <c r="R3" t="n">
-        <v>6568588.077439586</v>
+        <v>6568597</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,21 +845,11 @@
           <t>2012-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Strandsnår</t>
+          <t>nedskurenbäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,6 +876,649 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3334610</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Eskilns sydostsida, 1,5 km syd Ekholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387525</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6568597</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>nedskurenbäck</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>53973790</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nolbyviken väst om, 580 m sv Tappholmens spets, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>387531</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6568249</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nedre delen av brantare sluttning mot NNV</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rikare fläck i nedre delen av sluttning</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4961357</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eskilns ostsida 1,4 km syd Ekholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>387673</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568588</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Strandsnår</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>53973908</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nolbyviken väst om, 580 m sv Tappholmens spets, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>387531</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Nedre delen i brantare sluttning</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5287184</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eskilns ostsida 1,4 km syd Ekholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387673</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568588</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Strandsnår</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pär Dahlström, Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>53974070</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nolbyviken väst om, 580 m sv Tappholmens spets, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>387531</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568249</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>fåtalig</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>dal</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59469-2025 artfynd.xlsx
+++ b/artfynd/A 59469-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436303</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436304</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3334610</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53973790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4961357</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53973908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5287184</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,8 +1559,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53974070</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>